--- a/data/_materials.xlsx
+++ b/data/_materials.xlsx
@@ -15020,10 +15020,10 @@
         <v>41236.755</v>
       </c>
       <c r="C249">
-        <v>4675.343999999999</v>
+        <v>4675.344</v>
       </c>
       <c r="D249">
-        <v>3477.663999999999</v>
+        <v>3477.664</v>
       </c>
       <c r="E249">
         <v>1197.68</v>
@@ -16052,7 +16052,7 @@
         <v>1738.8</v>
       </c>
       <c r="E276">
-        <v>586.3399999999999</v>
+        <v>586.34</v>
       </c>
       <c r="F276">
         <v>10000</v>
@@ -16654,10 +16654,10 @@
         <v>52189.691</v>
       </c>
       <c r="C292">
-        <v>4689.143999999999</v>
+        <v>4689.144</v>
       </c>
       <c r="D292">
-        <v>3481.463999999999</v>
+        <v>3481.464</v>
       </c>
       <c r="E292">
         <v>1207.68</v>
@@ -17338,10 +17338,10 @@
         <v>74645.507</v>
       </c>
       <c r="C310">
-        <v>9350.687999999998</v>
+        <v>9350.688</v>
       </c>
       <c r="D310">
-        <v>6955.327999999999</v>
+        <v>6955.328</v>
       </c>
       <c r="E310">
         <v>2395.36</v>
@@ -18142,7 +18142,7 @@
         <v>1738.8</v>
       </c>
       <c r="E331">
-        <v>586.3399999999999</v>
+        <v>586.34</v>
       </c>
       <c r="F331">
         <v>10000</v>
@@ -49679,7 +49679,7 @@
         <v>4675.28</v>
       </c>
       <c r="D1161">
-        <v>3477.6</v>
+        <v>3477.599999999999</v>
       </c>
       <c r="E1161">
         <v>1197.68</v>

--- a/data/_materials.xlsx
+++ b/data/_materials.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/data/_materials.xlsx
+++ b/data/_materials.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="DOS" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/data/_materials.xlsx
+++ b/data/_materials.xlsx
@@ -8522,7 +8522,7 @@
         <v>6491</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -8534,10 +8534,10 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>6491</v>
+        <v>6449</v>
       </c>
       <c r="H78">
-        <v>6491</v>
+        <v>6449</v>
       </c>
       <c r="I78">
         <v>3280</v>
@@ -8902,7 +8902,7 @@
         <v>12700.47</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>128.016</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -8914,10 +8914,10 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>12700.47</v>
+        <v>12572.454</v>
       </c>
       <c r="H88">
-        <v>12700.47</v>
+        <v>12572.454</v>
       </c>
       <c r="I88">
         <v>10000</v>
@@ -9890,7 +9890,7 @@
         <v>158</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -9902,10 +9902,10 @@
         <v>0</v>
       </c>
       <c r="G114">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H114">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I114">
         <v>50</v>
@@ -10498,7 +10498,7 @@
         <v>130</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -10510,10 +10510,10 @@
         <v>0</v>
       </c>
       <c r="G130">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H130">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I130">
         <v>50</v>
@@ -13804,7 +13804,7 @@
         <v>3460</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -13816,10 +13816,10 @@
         <v>0</v>
       </c>
       <c r="G217">
-        <v>3460</v>
+        <v>3455</v>
       </c>
       <c r="H217">
-        <v>3460</v>
+        <v>3455</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>8438</v>
       </c>
       <c r="C219">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -13892,10 +13892,10 @@
         <v>0</v>
       </c>
       <c r="G219">
-        <v>8438</v>
+        <v>8433</v>
       </c>
       <c r="H219">
-        <v>8438</v>
+        <v>8433</v>
       </c>
       <c r="I219">
         <v>1000</v>
@@ -14108,7 +14108,7 @@
         <v>691</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="G225">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="H225">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="I225">
         <v>250</v>
@@ -14260,7 +14260,7 @@
         <v>1467</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -14272,10 +14272,10 @@
         <v>0</v>
       </c>
       <c r="G229">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="H229">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="I229">
         <v>1000</v>
@@ -14374,7 +14374,7 @@
         <v>1583</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -14386,10 +14386,10 @@
         <v>0</v>
       </c>
       <c r="G232">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H232">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="I232">
         <v>1000</v>
@@ -15041,7 +15041,7 @@
         <v>20000</v>
       </c>
       <c r="J249">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="K249">
         <v>0</v>
@@ -15400,7 +15400,7 @@
         <v>8601.321</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D259">
         <v>0</v>
@@ -15412,10 +15412,10 @@
         <v>0</v>
       </c>
       <c r="G259">
-        <v>8601.321</v>
+        <v>8571.321</v>
       </c>
       <c r="H259">
-        <v>8601.321</v>
+        <v>8571.321</v>
       </c>
       <c r="I259">
         <v>2800</v>
@@ -16198,7 +16198,7 @@
         <v>14402</v>
       </c>
       <c r="C280">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="D280">
         <v>0</v>
@@ -16210,10 +16210,10 @@
         <v>0</v>
       </c>
       <c r="G280">
-        <v>14402</v>
+        <v>14296</v>
       </c>
       <c r="H280">
-        <v>14402</v>
+        <v>14296</v>
       </c>
       <c r="I280">
         <v>5000</v>
@@ -17262,7 +17262,7 @@
         <v>1851.334</v>
       </c>
       <c r="C308">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -17274,10 +17274,10 @@
         <v>4704</v>
       </c>
       <c r="G308">
-        <v>6555.334</v>
+        <v>6100.334</v>
       </c>
       <c r="H308">
-        <v>6555.334</v>
+        <v>6100.334</v>
       </c>
       <c r="I308">
         <v>2500</v>
@@ -17490,7 +17490,7 @@
         <v>6932.986</v>
       </c>
       <c r="C314">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D314">
         <v>0</v>
@@ -17502,10 +17502,10 @@
         <v>300</v>
       </c>
       <c r="G314">
-        <v>7232.986</v>
+        <v>7171.986</v>
       </c>
       <c r="H314">
-        <v>7232.986</v>
+        <v>7171.986</v>
       </c>
       <c r="I314">
         <v>5000</v>
@@ -18440,7 +18440,7 @@
         <v>2987.916</v>
       </c>
       <c r="C339">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="D339">
         <v>0</v>
@@ -18452,10 +18452,10 @@
         <v>0</v>
       </c>
       <c r="G339">
-        <v>2987.916</v>
+        <v>2847.916</v>
       </c>
       <c r="H339">
-        <v>2987.916</v>
+        <v>2847.916</v>
       </c>
       <c r="I339">
         <v>2500</v>
@@ -18630,7 +18630,7 @@
         <v>775</v>
       </c>
       <c r="C344">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D344">
         <v>0</v>
@@ -18642,10 +18642,10 @@
         <v>0</v>
       </c>
       <c r="G344">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="H344">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="I344">
         <v>200</v>
@@ -18668,7 +18668,7 @@
         <v>2215</v>
       </c>
       <c r="C345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D345">
         <v>0</v>
@@ -18680,10 +18680,10 @@
         <v>0</v>
       </c>
       <c r="G345">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="H345">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="I345">
         <v>200</v>
@@ -18820,7 +18820,7 @@
         <v>3615.586</v>
       </c>
       <c r="C349">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D349">
         <v>0</v>
@@ -18832,10 +18832,10 @@
         <v>0</v>
       </c>
       <c r="G349">
-        <v>3615.586</v>
+        <v>3554.586</v>
       </c>
       <c r="H349">
-        <v>3615.586</v>
+        <v>3554.586</v>
       </c>
       <c r="I349">
         <v>1000</v>
@@ -19162,7 +19162,7 @@
         <v>1022.586</v>
       </c>
       <c r="C358">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D358">
         <v>0</v>
@@ -19174,10 +19174,10 @@
         <v>0</v>
       </c>
       <c r="G358">
-        <v>1022.586</v>
+        <v>961.586</v>
       </c>
       <c r="H358">
-        <v>1022.586</v>
+        <v>961.586</v>
       </c>
       <c r="I358">
         <v>2000</v>
@@ -20074,7 +20074,7 @@
         <v>10167.525</v>
       </c>
       <c r="C382">
-        <v>0</v>
+        <v>1782.9</v>
       </c>
       <c r="D382">
         <v>0</v>
@@ -20086,10 +20086,10 @@
         <v>0</v>
       </c>
       <c r="G382">
-        <v>10167.525</v>
+        <v>8384.625</v>
       </c>
       <c r="H382">
-        <v>10167.525</v>
+        <v>8384.625</v>
       </c>
       <c r="I382">
         <v>5000</v>
@@ -22126,7 +22126,7 @@
         <v>6575.856</v>
       </c>
       <c r="C436">
-        <v>0</v>
+        <v>2243</v>
       </c>
       <c r="D436">
         <v>0</v>
@@ -22138,10 +22138,10 @@
         <v>5280</v>
       </c>
       <c r="G436">
-        <v>11855.856</v>
+        <v>9612.856</v>
       </c>
       <c r="H436">
-        <v>11855.856</v>
+        <v>9612.856</v>
       </c>
       <c r="I436">
         <v>5280</v>
@@ -24824,7 +24824,7 @@
         <v>2679</v>
       </c>
       <c r="C507">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D507">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>0</v>
       </c>
       <c r="G507">
-        <v>2679</v>
+        <v>2229</v>
       </c>
       <c r="H507">
-        <v>2679</v>
+        <v>2229</v>
       </c>
       <c r="I507">
         <v>1000</v>
@@ -24976,7 +24976,7 @@
         <v>192.2</v>
       </c>
       <c r="C511">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="D511">
         <v>0</v>
@@ -24988,10 +24988,10 @@
         <v>0</v>
       </c>
       <c r="G511">
-        <v>192.2</v>
+        <v>180.95</v>
       </c>
       <c r="H511">
-        <v>192.2</v>
+        <v>180.95</v>
       </c>
       <c r="I511">
         <v>100</v>
@@ -25052,7 +25052,7 @@
         <v>2252</v>
       </c>
       <c r="C513">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D513">
         <v>0</v>
@@ -25064,10 +25064,10 @@
         <v>0</v>
       </c>
       <c r="G513">
-        <v>2252</v>
+        <v>2202</v>
       </c>
       <c r="H513">
-        <v>2252</v>
+        <v>2202</v>
       </c>
       <c r="I513">
         <v>500</v>
@@ -25090,7 +25090,7 @@
         <v>503.23</v>
       </c>
       <c r="C514">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="D514">
         <v>0</v>
@@ -25102,10 +25102,10 @@
         <v>0</v>
       </c>
       <c r="G514">
-        <v>503.23</v>
+        <v>491.98</v>
       </c>
       <c r="H514">
-        <v>503.23</v>
+        <v>491.98</v>
       </c>
       <c r="I514">
         <v>400</v>
@@ -25128,7 +25128,7 @@
         <v>1476</v>
       </c>
       <c r="C515">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D515">
         <v>0</v>
@@ -25140,10 +25140,10 @@
         <v>0</v>
       </c>
       <c r="G515">
-        <v>1476</v>
+        <v>1426</v>
       </c>
       <c r="H515">
-        <v>1476</v>
+        <v>1426</v>
       </c>
       <c r="I515">
         <v>500</v>
@@ -25280,7 +25280,7 @@
         <v>7251</v>
       </c>
       <c r="C519">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D519">
         <v>0</v>
@@ -25292,10 +25292,10 @@
         <v>0</v>
       </c>
       <c r="G519">
-        <v>7251</v>
+        <v>6801</v>
       </c>
       <c r="H519">
-        <v>7251</v>
+        <v>6801</v>
       </c>
       <c r="I519">
         <v>3000</v>
@@ -25356,7 +25356,7 @@
         <v>3530</v>
       </c>
       <c r="C521">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D521">
         <v>0</v>
@@ -25368,10 +25368,10 @@
         <v>0</v>
       </c>
       <c r="G521">
-        <v>3530</v>
+        <v>3080</v>
       </c>
       <c r="H521">
-        <v>3530</v>
+        <v>3080</v>
       </c>
       <c r="I521">
         <v>1000</v>
@@ -25432,7 +25432,7 @@
         <v>2274</v>
       </c>
       <c r="C523">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="D523">
         <v>0</v>
@@ -25444,10 +25444,10 @@
         <v>0</v>
       </c>
       <c r="G523">
-        <v>2274</v>
+        <v>1824</v>
       </c>
       <c r="H523">
-        <v>2274</v>
+        <v>1824</v>
       </c>
       <c r="I523">
         <v>1000</v>
@@ -27066,7 +27066,7 @@
         <v>2550.07</v>
       </c>
       <c r="C566">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="D566">
         <v>0</v>
@@ -27078,10 +27078,10 @@
         <v>2500</v>
       </c>
       <c r="G566">
-        <v>5050.07</v>
+        <v>4756.07</v>
       </c>
       <c r="H566">
-        <v>5050.07</v>
+        <v>4756.07</v>
       </c>
       <c r="I566">
         <v>2500</v>
@@ -27332,7 +27332,7 @@
         <v>2823</v>
       </c>
       <c r="C573">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="D573">
         <v>0</v>
@@ -27344,10 +27344,10 @@
         <v>0</v>
       </c>
       <c r="G573">
-        <v>2823</v>
+        <v>2529</v>
       </c>
       <c r="H573">
-        <v>2823</v>
+        <v>2529</v>
       </c>
       <c r="I573">
         <v>2500</v>
@@ -28548,7 +28548,7 @@
         <v>109</v>
       </c>
       <c r="C605">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D605">
         <v>0</v>
@@ -28560,10 +28560,10 @@
         <v>100</v>
       </c>
       <c r="G605">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="H605">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="I605">
         <v>100</v>
@@ -28624,7 +28624,7 @@
         <v>763</v>
       </c>
       <c r="C607">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D607">
         <v>0</v>
@@ -28636,10 +28636,10 @@
         <v>0</v>
       </c>
       <c r="G607">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="H607">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="I607">
         <v>500</v>
@@ -28928,7 +28928,7 @@
         <v>11</v>
       </c>
       <c r="C615">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D615">
         <v>0</v>
@@ -28940,10 +28940,10 @@
         <v>20</v>
       </c>
       <c r="G615">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H615">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I615">
         <v>20</v>
@@ -29878,7 +29878,7 @@
         <v>50</v>
       </c>
       <c r="C640">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D640">
         <v>0</v>
@@ -29890,10 +29890,10 @@
         <v>0</v>
       </c>
       <c r="G640">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H640">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="I640">
         <v>0</v>
@@ -29916,7 +29916,7 @@
         <v>552</v>
       </c>
       <c r="C641">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D641">
         <v>0</v>
@@ -29928,10 +29928,10 @@
         <v>0</v>
       </c>
       <c r="G641">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="H641">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="I641">
         <v>250</v>
@@ -30106,7 +30106,7 @@
         <v>595</v>
       </c>
       <c r="C646">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D646">
         <v>0</v>
@@ -30118,10 +30118,10 @@
         <v>156</v>
       </c>
       <c r="G646">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="H646">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="I646">
         <v>100</v>
@@ -30372,7 +30372,7 @@
         <v>1236</v>
       </c>
       <c r="C653">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D653">
         <v>0</v>
@@ -30384,10 +30384,10 @@
         <v>0</v>
       </c>
       <c r="G653">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="H653">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="I653">
         <v>1500</v>
@@ -30524,7 +30524,7 @@
         <v>171</v>
       </c>
       <c r="C657">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D657">
         <v>0</v>
@@ -30536,10 +30536,10 @@
         <v>504</v>
       </c>
       <c r="G657">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="H657">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="I657">
         <v>1500</v>
@@ -34096,7 +34096,7 @@
         <v>3194.882</v>
       </c>
       <c r="C751">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="D751">
         <v>0</v>
@@ -34108,10 +34108,10 @@
         <v>0</v>
       </c>
       <c r="G751">
-        <v>3194.882</v>
+        <v>3056.882</v>
       </c>
       <c r="H751">
-        <v>3194.882</v>
+        <v>3056.882</v>
       </c>
       <c r="I751">
         <v>1980</v>
@@ -34400,7 +34400,7 @@
         <v>1286.12</v>
       </c>
       <c r="C759">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D759">
         <v>0</v>
@@ -34412,10 +34412,10 @@
         <v>0</v>
       </c>
       <c r="G759">
-        <v>1286.12</v>
+        <v>1254.12</v>
       </c>
       <c r="H759">
-        <v>1286.12</v>
+        <v>1254.12</v>
       </c>
       <c r="I759">
         <v>1000</v>
@@ -36984,7 +36984,7 @@
         <v>47</v>
       </c>
       <c r="C827">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D827">
         <v>0</v>
@@ -36996,10 +36996,10 @@
         <v>0</v>
       </c>
       <c r="G827">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H827">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I827">
         <v>30</v>
@@ -38124,7 +38124,7 @@
         <v>33</v>
       </c>
       <c r="C857">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D857">
         <v>0</v>
@@ -38136,10 +38136,10 @@
         <v>50</v>
       </c>
       <c r="G857">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="H857">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="I857">
         <v>0</v>
@@ -38200,7 +38200,7 @@
         <v>49</v>
       </c>
       <c r="C859">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D859">
         <v>0</v>
@@ -38212,10 +38212,10 @@
         <v>0</v>
       </c>
       <c r="G859">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H859">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I859">
         <v>0</v>
@@ -38466,7 +38466,7 @@
         <v>174.657</v>
       </c>
       <c r="C866">
-        <v>0</v>
+        <v>3.982</v>
       </c>
       <c r="D866">
         <v>0</v>
@@ -38478,10 +38478,10 @@
         <v>0</v>
       </c>
       <c r="G866">
-        <v>174.657</v>
+        <v>170.675</v>
       </c>
       <c r="H866">
-        <v>174.657</v>
+        <v>170.675</v>
       </c>
       <c r="I866">
         <v>0</v>
@@ -38542,7 +38542,7 @@
         <v>175</v>
       </c>
       <c r="C868">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D868">
         <v>0</v>
@@ -38554,10 +38554,10 @@
         <v>0</v>
       </c>
       <c r="G868">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H868">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I868">
         <v>0</v>
@@ -38618,7 +38618,7 @@
         <v>684</v>
       </c>
       <c r="C870">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D870">
         <v>0</v>
@@ -38630,10 +38630,10 @@
         <v>0</v>
       </c>
       <c r="G870">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="H870">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="I870">
         <v>0</v>
@@ -38732,7 +38732,7 @@
         <v>125</v>
       </c>
       <c r="C873">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D873">
         <v>0</v>
@@ -38744,10 +38744,10 @@
         <v>0</v>
       </c>
       <c r="G873">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H873">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I873">
         <v>0</v>
@@ -38808,7 +38808,7 @@
         <v>145</v>
       </c>
       <c r="C875">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D875">
         <v>0</v>
@@ -38820,10 +38820,10 @@
         <v>0</v>
       </c>
       <c r="G875">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H875">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I875">
         <v>0</v>
@@ -40214,7 +40214,7 @@
         <v>357</v>
       </c>
       <c r="C912">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D912">
         <v>0</v>
@@ -40226,10 +40226,10 @@
         <v>0</v>
       </c>
       <c r="G912">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="H912">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="I912">
         <v>25</v>
@@ -40252,7 +40252,7 @@
         <v>464</v>
       </c>
       <c r="C913">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D913">
         <v>0</v>
@@ -40264,10 +40264,10 @@
         <v>0</v>
       </c>
       <c r="G913">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="H913">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="I913">
         <v>200</v>
@@ -46370,7 +46370,7 @@
         <v>199</v>
       </c>
       <c r="C1074">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D1074">
         <v>0</v>
@@ -46382,10 +46382,10 @@
         <v>0</v>
       </c>
       <c r="G1074">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H1074">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I1074">
         <v>0</v>
@@ -46788,7 +46788,7 @@
         <v>15016.47</v>
       </c>
       <c r="C1085">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="D1085">
         <v>0</v>
@@ -46800,10 +46800,10 @@
         <v>0</v>
       </c>
       <c r="G1085">
-        <v>15016.47</v>
+        <v>14407.47</v>
       </c>
       <c r="H1085">
-        <v>15016.47</v>
+        <v>14407.47</v>
       </c>
       <c r="I1085">
         <v>10000</v>
@@ -47738,7 +47738,7 @@
         <v>8551.348</v>
       </c>
       <c r="C1110">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D1110">
         <v>0</v>
@@ -47750,10 +47750,10 @@
         <v>0</v>
       </c>
       <c r="G1110">
-        <v>8551.348</v>
+        <v>8451.348</v>
       </c>
       <c r="H1110">
-        <v>8551.348</v>
+        <v>8451.348</v>
       </c>
       <c r="I1110">
         <v>10000</v>
@@ -48194,7 +48194,7 @@
         <v>4045</v>
       </c>
       <c r="C1122">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D1122">
         <v>0</v>
@@ -48206,10 +48206,10 @@
         <v>0</v>
       </c>
       <c r="G1122">
-        <v>4045</v>
+        <v>4021</v>
       </c>
       <c r="H1122">
-        <v>4045</v>
+        <v>4021</v>
       </c>
       <c r="I1122">
         <v>0</v>
@@ -50778,7 +50778,7 @@
         <v>131850.044</v>
       </c>
       <c r="C1190">
-        <v>0</v>
+        <v>3621.834</v>
       </c>
       <c r="D1190">
         <v>0</v>
@@ -50790,10 +50790,10 @@
         <v>0</v>
       </c>
       <c r="G1190">
-        <v>131850.044</v>
+        <v>128228.21</v>
       </c>
       <c r="H1190">
-        <v>131850.044</v>
+        <v>128228.21</v>
       </c>
       <c r="I1190">
         <v>125000</v>
@@ -58378,7 +58378,7 @@
         <v>21</v>
       </c>
       <c r="C1390">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1390">
         <v>0</v>
@@ -58390,10 +58390,10 @@
         <v>0</v>
       </c>
       <c r="G1390">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H1390">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I1390">
         <v>20</v>
@@ -59100,7 +59100,7 @@
         <v>21003.822</v>
       </c>
       <c r="C1409">
-        <v>0</v>
+        <v>742.284</v>
       </c>
       <c r="D1409">
         <v>0</v>
@@ -59112,10 +59112,10 @@
         <v>0</v>
       </c>
       <c r="G1409">
-        <v>21003.822</v>
+        <v>20261.538</v>
       </c>
       <c r="H1409">
-        <v>21003.822</v>
+        <v>20261.538</v>
       </c>
       <c r="I1409">
         <v>15000</v>
@@ -60012,7 +60012,7 @@
         <v>20000</v>
       </c>
       <c r="C1433">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="D1433">
         <v>0</v>
@@ -60024,10 +60024,10 @@
         <v>0</v>
       </c>
       <c r="G1433">
-        <v>20000</v>
+        <v>19250</v>
       </c>
       <c r="H1433">
-        <v>20000</v>
+        <v>19250</v>
       </c>
       <c r="I1433">
         <v>0</v>
@@ -62520,7 +62520,7 @@
         <v>21069.32</v>
       </c>
       <c r="C1499">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="D1499">
         <v>0</v>
@@ -62532,10 +62532,10 @@
         <v>0</v>
       </c>
       <c r="G1499">
-        <v>21069.32</v>
+        <v>20628.32</v>
       </c>
       <c r="H1499">
-        <v>21069.32</v>
+        <v>20628.32</v>
       </c>
       <c r="I1499">
         <v>10000</v>
@@ -62558,7 +62558,7 @@
         <v>15396.19</v>
       </c>
       <c r="C1500">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="D1500">
         <v>0</v>
@@ -62570,10 +62570,10 @@
         <v>0</v>
       </c>
       <c r="G1500">
-        <v>15396.19</v>
+        <v>15102.19</v>
       </c>
       <c r="H1500">
-        <v>15396.19</v>
+        <v>15102.19</v>
       </c>
       <c r="I1500">
         <v>7500</v>
@@ -62672,7 +62672,7 @@
         <v>28409.9</v>
       </c>
       <c r="C1503">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D1503">
         <v>0</v>
@@ -62684,10 +62684,10 @@
         <v>0</v>
       </c>
       <c r="G1503">
-        <v>28409.9</v>
+        <v>28397.9</v>
       </c>
       <c r="H1503">
-        <v>28409.9</v>
+        <v>28397.9</v>
       </c>
       <c r="I1503">
         <v>20000</v>
@@ -62786,7 +62786,7 @@
         <v>4632.33</v>
       </c>
       <c r="C1506">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D1506">
         <v>0</v>
@@ -62798,10 +62798,10 @@
         <v>0</v>
       </c>
       <c r="G1506">
-        <v>4632.33</v>
+        <v>4620.33</v>
       </c>
       <c r="H1506">
-        <v>4632.33</v>
+        <v>4620.33</v>
       </c>
       <c r="I1506">
         <v>2500</v>
@@ -62824,7 +62824,7 @@
         <v>6731.57</v>
       </c>
       <c r="C1507">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="D1507">
         <v>0</v>
@@ -62836,10 +62836,10 @@
         <v>0</v>
       </c>
       <c r="G1507">
-        <v>6731.57</v>
+        <v>6290.57</v>
       </c>
       <c r="H1507">
-        <v>6731.57</v>
+        <v>6290.57</v>
       </c>
       <c r="I1507">
         <v>2500</v>
@@ -62862,7 +62862,7 @@
         <v>4908.06</v>
       </c>
       <c r="C1508">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="D1508">
         <v>0</v>
@@ -62874,10 +62874,10 @@
         <v>0</v>
       </c>
       <c r="G1508">
-        <v>4908.06</v>
+        <v>4467.06</v>
       </c>
       <c r="H1508">
-        <v>4908.06</v>
+        <v>4467.06</v>
       </c>
       <c r="I1508">
         <v>2500</v>
@@ -63242,7 +63242,7 @@
         <v>20353.69</v>
       </c>
       <c r="C1518">
-        <v>0</v>
+        <v>2879.55</v>
       </c>
       <c r="D1518">
         <v>0</v>
@@ -63254,10 +63254,10 @@
         <v>0</v>
       </c>
       <c r="G1518">
-        <v>20353.69</v>
+        <v>17474.14</v>
       </c>
       <c r="H1518">
-        <v>20353.69</v>
+        <v>17474.14</v>
       </c>
       <c r="I1518">
         <v>15000</v>
@@ -63356,7 +63356,7 @@
         <v>23443.333</v>
       </c>
       <c r="C1521">
-        <v>0</v>
+        <v>36.6</v>
       </c>
       <c r="D1521">
         <v>0</v>
@@ -63368,10 +63368,10 @@
         <v>0</v>
       </c>
       <c r="G1521">
-        <v>23443.333</v>
+        <v>23406.733</v>
       </c>
       <c r="H1521">
-        <v>23443.333</v>
+        <v>23406.733</v>
       </c>
       <c r="I1521">
         <v>15000</v>
@@ -63546,7 +63546,7 @@
         <v>279.143</v>
       </c>
       <c r="C1526">
-        <v>0</v>
+        <v>152.996</v>
       </c>
       <c r="D1526">
         <v>0</v>
@@ -63558,10 +63558,10 @@
         <v>0</v>
       </c>
       <c r="G1526">
-        <v>279.143</v>
+        <v>126.147</v>
       </c>
       <c r="H1526">
-        <v>279.143</v>
+        <v>126.147</v>
       </c>
       <c r="I1526">
         <v>100</v>
@@ -63698,7 +63698,7 @@
         <v>363.675</v>
       </c>
       <c r="C1530">
-        <v>0</v>
+        <v>216.19</v>
       </c>
       <c r="D1530">
         <v>0</v>
@@ -63710,10 +63710,10 @@
         <v>100</v>
       </c>
       <c r="G1530">
-        <v>463.675</v>
+        <v>247.485</v>
       </c>
       <c r="H1530">
-        <v>463.675</v>
+        <v>247.485</v>
       </c>
       <c r="I1530">
         <v>250</v>
@@ -63736,7 +63736,7 @@
         <v>3737</v>
       </c>
       <c r="C1531">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D1531">
         <v>0</v>
@@ -63748,10 +63748,10 @@
         <v>0</v>
       </c>
       <c r="G1531">
-        <v>3737</v>
+        <v>3550</v>
       </c>
       <c r="H1531">
-        <v>3737</v>
+        <v>3550</v>
       </c>
       <c r="I1531">
         <v>2500</v>
@@ -63850,7 +63850,7 @@
         <v>445.473</v>
       </c>
       <c r="C1534">
-        <v>0</v>
+        <v>216.19</v>
       </c>
       <c r="D1534">
         <v>0</v>
@@ -63862,10 +63862,10 @@
         <v>100</v>
       </c>
       <c r="G1534">
-        <v>545.473</v>
+        <v>329.283</v>
       </c>
       <c r="H1534">
-        <v>545.473</v>
+        <v>329.283</v>
       </c>
       <c r="I1534">
         <v>250</v>
@@ -63888,7 +63888,7 @@
         <v>94.038</v>
       </c>
       <c r="C1535">
-        <v>0</v>
+        <v>26.608</v>
       </c>
       <c r="D1535">
         <v>0</v>
@@ -63900,10 +63900,10 @@
         <v>0</v>
       </c>
       <c r="G1535">
-        <v>94.038</v>
+        <v>67.42999999999999</v>
       </c>
       <c r="H1535">
-        <v>94.038</v>
+        <v>67.42999999999999</v>
       </c>
       <c r="I1535">
         <v>0</v>
@@ -63964,7 +63964,7 @@
         <v>875</v>
       </c>
       <c r="C1537">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="D1537">
         <v>0</v>
@@ -63976,10 +63976,10 @@
         <v>1000</v>
       </c>
       <c r="G1537">
-        <v>1875</v>
+        <v>1222</v>
       </c>
       <c r="H1537">
-        <v>1875</v>
+        <v>1222</v>
       </c>
       <c r="I1537">
         <v>500</v>
@@ -64002,7 +64002,7 @@
         <v>12736.177</v>
       </c>
       <c r="C1538">
-        <v>0</v>
+        <v>3326</v>
       </c>
       <c r="D1538">
         <v>0</v>
@@ -64014,10 +64014,10 @@
         <v>0</v>
       </c>
       <c r="G1538">
-        <v>12736.177</v>
+        <v>9410.177</v>
       </c>
       <c r="H1538">
-        <v>12736.177</v>
+        <v>9410.177</v>
       </c>
       <c r="I1538">
         <v>500</v>
@@ -64116,7 +64116,7 @@
         <v>56.61</v>
       </c>
       <c r="C1541">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="D1541">
         <v>0</v>
@@ -64128,10 +64128,10 @@
         <v>0</v>
       </c>
       <c r="G1541">
-        <v>56.61</v>
+        <v>54.69</v>
       </c>
       <c r="H1541">
-        <v>56.61</v>
+        <v>54.69</v>
       </c>
       <c r="I1541">
         <v>5</v>
@@ -64306,7 +64306,7 @@
         <v>1475.13</v>
       </c>
       <c r="C1546">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="D1546">
         <v>0</v>
@@ -64318,10 +64318,10 @@
         <v>0</v>
       </c>
       <c r="G1546">
-        <v>1475.13</v>
+        <v>1369.13</v>
       </c>
       <c r="H1546">
-        <v>1475.13</v>
+        <v>1369.13</v>
       </c>
       <c r="I1546">
         <v>0</v>
@@ -66548,7 +66548,7 @@
         <v>551.008</v>
       </c>
       <c r="C1605">
-        <v>0</v>
+        <v>3.982</v>
       </c>
       <c r="D1605">
         <v>0</v>
@@ -66560,10 +66560,10 @@
         <v>0</v>
       </c>
       <c r="G1605">
-        <v>551.008</v>
+        <v>547.0260000000001</v>
       </c>
       <c r="H1605">
-        <v>551.008</v>
+        <v>547.0260000000001</v>
       </c>
       <c r="I1605">
         <v>250</v>
@@ -67878,7 +67878,7 @@
         <v>3948.173</v>
       </c>
       <c r="C1640">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="D1640">
         <v>0</v>
@@ -67890,10 +67890,10 @@
         <v>0</v>
       </c>
       <c r="G1640">
-        <v>3948.173</v>
+        <v>3810.173</v>
       </c>
       <c r="H1640">
-        <v>3948.173</v>
+        <v>3810.173</v>
       </c>
       <c r="I1640">
         <v>2500</v>
@@ -68638,7 +68638,7 @@
         <v>3578.45</v>
       </c>
       <c r="C1660">
-        <v>0</v>
+        <v>2171</v>
       </c>
       <c r="D1660">
         <v>0</v>
@@ -68650,10 +68650,10 @@
         <v>0</v>
       </c>
       <c r="G1660">
-        <v>3578.45</v>
+        <v>1407.45</v>
       </c>
       <c r="H1660">
-        <v>3578.45</v>
+        <v>1407.45</v>
       </c>
       <c r="I1660">
         <v>5000</v>
@@ -69094,7 +69094,7 @@
         <v>26999.96</v>
       </c>
       <c r="C1672">
-        <v>0</v>
+        <v>2171</v>
       </c>
       <c r="D1672">
         <v>0</v>
@@ -69106,10 +69106,10 @@
         <v>0</v>
       </c>
       <c r="G1672">
-        <v>26999.96</v>
+        <v>24828.96</v>
       </c>
       <c r="H1672">
-        <v>26999.96</v>
+        <v>24828.96</v>
       </c>
       <c r="I1672">
         <v>5000</v>
@@ -69740,7 +69740,7 @@
         <v>161</v>
       </c>
       <c r="C1689">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1689">
         <v>0</v>
@@ -69752,10 +69752,10 @@
         <v>0</v>
       </c>
       <c r="G1689">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H1689">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I1689">
         <v>0</v>
@@ -70386,7 +70386,7 @@
         <v>31613.642</v>
       </c>
       <c r="C1706">
-        <v>0</v>
+        <v>5084.55</v>
       </c>
       <c r="D1706">
         <v>0</v>
@@ -70398,10 +70398,10 @@
         <v>0</v>
       </c>
       <c r="G1706">
-        <v>31613.642</v>
+        <v>26529.092</v>
       </c>
       <c r="H1706">
-        <v>31613.642</v>
+        <v>26529.092</v>
       </c>
       <c r="I1706">
         <v>25000</v>
@@ -70538,7 +70538,7 @@
         <v>3330</v>
       </c>
       <c r="C1710">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D1710">
         <v>0</v>
@@ -70550,10 +70550,10 @@
         <v>0</v>
       </c>
       <c r="G1710">
-        <v>3330</v>
+        <v>3130</v>
       </c>
       <c r="H1710">
-        <v>3330</v>
+        <v>3130</v>
       </c>
       <c r="I1710">
         <v>2500</v>

--- a/data/_materials.xlsx
+++ b/data/_materials.xlsx
@@ -15041,7 +15041,7 @@
         <v>20000</v>
       </c>
       <c r="J249">
-        <v>100000</v>
+        <v>20010</v>
       </c>
       <c r="K249">
         <v>0</v>
